--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABED403B-FFA2-44B3-B11C-FCC9AA8980A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78145EDF-7F3D-4DC6-B290-918E1EF651F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1452,25 +1452,47 @@
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="A16" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B16" s="9">
+        <v>300</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>60</v>
+      </c>
+      <c r="E16" s="9">
+        <v>20</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>120</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
+        <v>940</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78145EDF-7F3D-4DC6-B290-918E1EF651F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F585145-DA62-46F5-B555-51B5D3FF35C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1496,25 +1496,47 @@
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="A17" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B17" s="9">
+        <v>290</v>
+      </c>
+      <c r="C17" s="9">
+        <v>90</v>
+      </c>
+      <c r="D17" s="9">
+        <v>50</v>
+      </c>
+      <c r="E17" s="9">
+        <v>10</v>
+      </c>
+      <c r="F17" s="9">
+        <v>150</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3</v>
+      </c>
+      <c r="H17" s="9">
+        <v>450</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
+        <v>400</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F585145-DA62-46F5-B555-51B5D3FF35C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2666ADCC-E0D6-42B6-B38E-20F1BAB5D614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,15 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>went home for rakhi</t>
+  </si>
+  <si>
+    <t>rahi</t>
+  </si>
+  <si>
+    <t>came back from home</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1016,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>46247</v>
       </c>
@@ -1540,158 +1549,318 @@
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="A18" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B18" s="9">
+        <v>400</v>
+      </c>
+      <c r="C18" s="9">
+        <v>60</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>30</v>
+      </c>
+      <c r="F18" s="9">
+        <v>350</v>
+      </c>
+      <c r="G18" s="9">
+        <v>7</v>
+      </c>
+      <c r="H18" s="9">
+        <v>120</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
+        <v>480</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+      <c r="A19" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B19" s="9">
+        <v>450</v>
+      </c>
+      <c r="C19" s="9">
+        <v>70</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <v>30</v>
+      </c>
+      <c r="F19" s="9">
+        <v>200</v>
+      </c>
+      <c r="G19" s="9">
+        <v>4</v>
+      </c>
+      <c r="H19" s="9">
+        <v>120</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>870</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
+        <v>570</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+      <c r="A20" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B20" s="9">
+        <v>410</v>
+      </c>
+      <c r="C20" s="9">
+        <v>60</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>45</v>
+      </c>
+      <c r="F20" s="9">
+        <v>350</v>
+      </c>
+      <c r="G20" s="9">
+        <v>7</v>
+      </c>
+      <c r="H20" s="9">
+        <v>320</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
+        <v>255</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+      <c r="A21" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B21" s="9">
+        <v>390</v>
+      </c>
+      <c r="C21" s="9">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9">
+        <v>60</v>
+      </c>
+      <c r="E21" s="9">
+        <v>45</v>
+      </c>
+      <c r="F21" s="9">
+        <v>100</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>450</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>335</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B22" s="9">
+        <v>640</v>
+      </c>
+      <c r="C22" s="9">
+        <v>120</v>
+      </c>
+      <c r="D22" s="9">
+        <v>120</v>
+      </c>
+      <c r="E22" s="9">
+        <v>60</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>350</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
+        <v>150</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+      <c r="A23" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B23" s="9">
+        <v>550</v>
+      </c>
+      <c r="C23" s="9">
+        <v>90</v>
+      </c>
+      <c r="D23" s="9">
+        <v>120</v>
+      </c>
+      <c r="E23" s="9">
+        <v>40</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>350</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
+        <v>290</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+      <c r="A24" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B24" s="9">
+        <v>60</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>60</v>
+      </c>
+      <c r="E24" s="9">
+        <v>30</v>
+      </c>
+      <c r="F24" s="9">
+        <v>100</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>120</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>370</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>1070</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2666ADCC-E0D6-42B6-B38E-20F1BAB5D614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D55F1B6-7B28-4431-93C4-EAE45CA82D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1821,7 +1821,7 @@
         <v>46265</v>
       </c>
       <c r="B24" s="9">
-        <v>60</v>
+        <v>660</v>
       </c>
       <c r="C24" s="9">
         <v>0</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v>370</v>
+        <v>970</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v>1070</v>
+        <v>470</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>49</v>
@@ -1863,73 +1863,141 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+      <c r="A25" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="9">
+        <v>470</v>
+      </c>
+      <c r="C25" s="9">
+        <v>60</v>
+      </c>
+      <c r="D25" s="9">
+        <v>60</v>
+      </c>
+      <c r="E25" s="9">
+        <v>30</v>
+      </c>
+      <c r="F25" s="9">
+        <v>350</v>
+      </c>
+      <c r="G25" s="9">
+        <v>7</v>
+      </c>
+      <c r="H25" s="9">
+        <v>60</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
+        <v>410</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B26" s="9">
+        <v>480</v>
+      </c>
+      <c r="C26" s="9">
+        <v>70</v>
+      </c>
+      <c r="D26" s="9">
+        <v>60</v>
+      </c>
+      <c r="E26" s="9">
+        <v>30</v>
+      </c>
+      <c r="F26" s="9">
+        <v>200</v>
+      </c>
+      <c r="G26" s="9">
+        <v>4</v>
+      </c>
+      <c r="H26" s="9">
+        <v>60</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>900</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
+        <v>540</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+      <c r="A27" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B27" s="9">
+        <v>500</v>
+      </c>
+      <c r="C27" s="9">
+        <v>70</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <v>350</v>
+      </c>
+      <c r="G27" s="9">
+        <v>7</v>
+      </c>
+      <c r="H27" s="9">
+        <v>60</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
+        <v>460</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
+      <c r="A28" s="8">
+        <v>46269</v>
+      </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D55F1B6-7B28-4431-93C4-EAE45CA82D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5600EAA2-3F52-4825-9E75-3C5AC6C4A3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1998,46 +1998,88 @@
       <c r="A28" s="8">
         <v>46269</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+      <c r="B28" s="9">
+        <v>450</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>300</v>
+      </c>
+      <c r="G28" s="9">
+        <v>6</v>
+      </c>
+      <c r="H28" s="9">
+        <v>120</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>870</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
+        <v>570</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+      <c r="A29" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B29" s="9">
+        <v>600</v>
+      </c>
+      <c r="C29" s="9">
+        <v>60</v>
+      </c>
+      <c r="D29" s="9">
+        <v>120</v>
+      </c>
+      <c r="E29" s="9">
+        <v>60</v>
+      </c>
+      <c r="F29" s="9">
+        <v>50</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>120</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
+        <v>430</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5600EAA2-3F52-4825-9E75-3C5AC6C4A3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABB7E08-43C2-4026-80D2-ABE20AD5B14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2083,91 +2083,179 @@
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+      <c r="A30" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="9">
+        <v>430</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>60</v>
+      </c>
+      <c r="E30" s="9">
+        <v>45</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>350</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>885</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
+        <v>555</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="A31" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="9">
+        <v>500</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>60</v>
+      </c>
+      <c r="E31" s="9">
+        <v>45</v>
+      </c>
+      <c r="F31" s="9">
+        <v>150</v>
+      </c>
+      <c r="G31" s="9">
+        <v>3</v>
+      </c>
+      <c r="H31" s="9">
+        <v>200</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>955</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
+        <v>485</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+      <c r="A32" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="9">
+        <v>420</v>
+      </c>
+      <c r="C32" s="9">
+        <v>60</v>
+      </c>
+      <c r="D32" s="9">
+        <v>60</v>
+      </c>
+      <c r="E32" s="9">
+        <v>30</v>
+      </c>
+      <c r="F32" s="9">
+        <v>350</v>
+      </c>
+      <c r="G32" s="9">
+        <v>7</v>
+      </c>
+      <c r="H32" s="9">
+        <v>450</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+      <c r="A33" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B33" s="9">
+        <v>400</v>
+      </c>
+      <c r="C33" s="9">
+        <v>60</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
+        <v>30</v>
+      </c>
+      <c r="F33" s="9">
+        <v>200</v>
+      </c>
+      <c r="G33" s="9">
+        <v>4</v>
+      </c>
+      <c r="H33" s="9">
+        <v>230</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>920</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
+        <v>520</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABB7E08-43C2-4026-80D2-ABE20AD5B14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D608D10A-82AF-4677-88C8-0CF8D6783B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2168,7 +2168,7 @@
       <c r="M31" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N31" s="12"/>
+      <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
@@ -2259,157 +2259,311 @@
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+      <c r="A34" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B34" s="9">
+        <v>380</v>
+      </c>
+      <c r="C34" s="9">
+        <v>70</v>
+      </c>
+      <c r="D34" s="9">
+        <v>60</v>
+      </c>
+      <c r="E34" s="9">
+        <v>45</v>
+      </c>
+      <c r="F34" s="9">
+        <v>350</v>
+      </c>
+      <c r="G34" s="9">
+        <v>5</v>
+      </c>
+      <c r="H34" s="9">
+        <v>200</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
+        <v>335</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+      <c r="A35" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="9">
+        <v>380</v>
+      </c>
+      <c r="C35" s="9">
+        <v>0</v>
+      </c>
+      <c r="D35" s="9">
+        <v>120</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9">
+        <v>300</v>
+      </c>
+      <c r="G35" s="9">
+        <v>4</v>
+      </c>
+      <c r="H35" s="9">
+        <v>350</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
+        <v>290</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+      <c r="A36" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B36" s="9">
+        <v>570</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9">
+        <v>60</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>60</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>690</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
+        <v>750</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+      <c r="A37" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B37" s="9">
+        <v>340</v>
+      </c>
+      <c r="C37" s="9">
+        <v>70</v>
+      </c>
+      <c r="D37" s="9">
+        <v>60</v>
+      </c>
+      <c r="E37" s="9">
+        <v>60</v>
+      </c>
+      <c r="F37" s="9">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
+      <c r="H37" s="9">
+        <v>70</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>600</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
+        <v>840</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+      <c r="A38" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B38" s="9">
+        <v>390</v>
+      </c>
+      <c r="C38" s="9">
+        <v>70</v>
+      </c>
+      <c r="D38" s="9">
+        <v>60</v>
+      </c>
+      <c r="E38" s="9">
+        <v>50</v>
+      </c>
+      <c r="F38" s="9">
+        <v>150</v>
+      </c>
+      <c r="G38" s="9">
+        <v>3</v>
+      </c>
+      <c r="H38" s="9">
+        <v>250</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
+        <v>470</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N38" s="12"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+      <c r="A39" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="9">
+        <v>460</v>
+      </c>
+      <c r="C39" s="9">
+        <v>80</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9">
+        <v>20</v>
+      </c>
+      <c r="F39" s="9">
+        <v>250</v>
+      </c>
+      <c r="G39" s="9">
+        <v>5</v>
+      </c>
+      <c r="H39" s="9">
+        <v>200</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
+        <v>430</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+      <c r="A40" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B40" s="9">
+        <v>420</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9">
+        <v>60</v>
+      </c>
+      <c r="E40" s="9">
+        <v>30</v>
+      </c>
+      <c r="F40" s="9">
+        <v>100</v>
+      </c>
+      <c r="G40" s="9">
+        <v>2</v>
+      </c>
+      <c r="H40" s="9">
+        <v>120</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>730</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
+        <v>710</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -10377,7 +10531,7 @@
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="N31 M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D608D10A-82AF-4677-88C8-0CF8D6783B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E0A641-51A7-4BF2-853E-7348B1610CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,13 +205,7 @@
     <t>August</t>
   </si>
   <si>
-    <t>Felt a bit tired after class and slept in the evening.</t>
-  </si>
-  <si>
     <t>Satisfied</t>
-  </si>
-  <si>
-    <t>independeance day</t>
   </si>
   <si>
     <t>High</t>
@@ -226,13 +220,10 @@
     <t>Very Satisfied</t>
   </si>
   <si>
-    <t>went home for rakhi</t>
+    <t>s</t>
   </si>
   <si>
-    <t>rahi</t>
-  </si>
-  <si>
-    <t>came back from home</t>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -886,7 +877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:T401"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -902,7 +893,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
@@ -920,7 +911,7 @@
       <c r="M1" s="19"/>
       <c r="N1" s="19"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -937,7 +928,7 @@
       </c>
       <c r="G2" s="21"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -954,7 +945,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
@@ -972,7 +963,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1015,8 +1006,11 @@
       <c r="N5" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>46247</v>
       </c>
@@ -1058,11 +1052,9 @@
       <c r="M6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N6" s="17"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>46248</v>
       </c>
@@ -1106,7 +1098,7 @@
       </c>
       <c r="N7" s="12"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>46249</v>
       </c>
@@ -1143,16 +1135,14 @@
         <v>49</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>46250</v>
       </c>
@@ -1189,14 +1179,14 @@
         <v>49</v>
       </c>
       <c r="L9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>59</v>
-      </c>
       <c r="N9" s="12"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>46251</v>
       </c>
@@ -1233,14 +1223,14 @@
         <v>52</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N10" s="12"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>46252</v>
       </c>
@@ -1280,11 +1270,11 @@
         <v>52</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>46253</v>
       </c>
@@ -1321,14 +1311,14 @@
         <v>49</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N12" s="12"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>46254</v>
       </c>
@@ -1365,14 +1355,14 @@
         <v>49</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>50</v>
       </c>
       <c r="N13" s="12"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>46255</v>
       </c>
@@ -1416,7 +1406,7 @@
       </c>
       <c r="N14" s="12"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>46256</v>
       </c>
@@ -1453,14 +1443,14 @@
         <v>49</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>50</v>
       </c>
       <c r="N15" s="12"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>46257</v>
       </c>
@@ -1494,13 +1484,13 @@
         <v>940</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N16" s="12"/>
     </row>
@@ -1541,10 +1531,10 @@
         <v>49</v>
       </c>
       <c r="L17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N17" s="12"/>
     </row>
@@ -1588,7 +1578,7 @@
         <v>52</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N18" s="12"/>
     </row>
@@ -1629,10 +1619,10 @@
         <v>49</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N19" s="12"/>
     </row>
@@ -1673,10 +1663,10 @@
         <v>49</v>
       </c>
       <c r="L20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N20" s="12"/>
     </row>
@@ -1717,14 +1707,12 @@
         <v>49</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N21" s="12" t="s">
-        <v>63</v>
-      </c>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
@@ -1760,7 +1748,7 @@
         <v>150</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L22" s="11" t="s">
         <v>52</v>
@@ -1768,9 +1756,7 @@
       <c r="M22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N22" s="12" t="s">
-        <v>64</v>
-      </c>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
@@ -1809,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>50</v>
@@ -1853,14 +1839,12 @@
         <v>49</v>
       </c>
       <c r="L24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M24" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>65</v>
-      </c>
+      <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
@@ -1987,10 +1971,10 @@
         <v>49</v>
       </c>
       <c r="L27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N27" s="12"/>
     </row>
@@ -2075,10 +2059,10 @@
         <v>49</v>
       </c>
       <c r="L29" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N29" s="12"/>
     </row>
@@ -2119,10 +2103,10 @@
         <v>49</v>
       </c>
       <c r="L30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N30" s="12"/>
     </row>
@@ -2207,10 +2191,10 @@
         <v>49</v>
       </c>
       <c r="L32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N32" s="12"/>
     </row>
@@ -2251,10 +2235,10 @@
         <v>49</v>
       </c>
       <c r="L33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N33" s="12"/>
     </row>
@@ -2339,10 +2323,10 @@
         <v>49</v>
       </c>
       <c r="L35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N35" s="12"/>
     </row>
@@ -2383,10 +2367,10 @@
         <v>49</v>
       </c>
       <c r="L36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N36" s="12"/>
     </row>
@@ -2471,10 +2455,10 @@
         <v>49</v>
       </c>
       <c r="L38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N38" s="12"/>
     </row>
@@ -2515,10 +2499,10 @@
         <v>49</v>
       </c>
       <c r="L39" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="M39" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="N39" s="12"/>
     </row>
@@ -2567,113 +2551,223 @@
       <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="A41" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="9">
+        <v>500</v>
+      </c>
+      <c r="C41" s="9">
+        <v>60</v>
+      </c>
+      <c r="D41" s="9">
+        <v>120</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9">
+        <v>350</v>
+      </c>
+      <c r="G41" s="9">
+        <v>7</v>
+      </c>
+      <c r="H41" s="9">
+        <v>120</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
+        <v>290</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="N41" s="12"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
+      <c r="A42" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="9">
+        <v>520</v>
+      </c>
+      <c r="C42" s="9">
+        <v>69</v>
+      </c>
+      <c r="D42" s="9">
+        <v>180</v>
+      </c>
+      <c r="E42" s="9">
+        <v>60</v>
+      </c>
+      <c r="F42" s="9">
+        <v>300</v>
+      </c>
+      <c r="G42" s="9">
+        <v>6</v>
+      </c>
+      <c r="H42" s="9">
+        <v>60</v>
+      </c>
+      <c r="I42" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
+        <v>1189</v>
+      </c>
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
+        <v>251</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+      <c r="A43" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B43" s="9">
+        <v>350</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9">
+        <v>180</v>
+      </c>
+      <c r="E43" s="9">
+        <v>35</v>
+      </c>
+      <c r="F43" s="9">
+        <v>100</v>
+      </c>
+      <c r="G43" s="9">
+        <v>2</v>
+      </c>
+      <c r="H43" s="9">
+        <v>120</v>
+      </c>
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+        <v>785</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
+        <v>655</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N43" s="12"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+      <c r="A44" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="9">
+        <v>350</v>
+      </c>
+      <c r="C44" s="9">
+        <v>120</v>
+      </c>
+      <c r="D44" s="9">
+        <v>100</v>
+      </c>
+      <c r="E44" s="9">
+        <v>50</v>
+      </c>
+      <c r="F44" s="9">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>60</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>680</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
+        <v>760</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+      <c r="A45" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="9">
+        <v>450</v>
+      </c>
+      <c r="C45" s="9">
+        <v>65</v>
+      </c>
+      <c r="D45" s="9">
+        <v>140</v>
+      </c>
+      <c r="E45" s="9">
+        <v>40</v>
+      </c>
+      <c r="F45" s="9">
+        <v>150</v>
+      </c>
+      <c r="G45" s="9">
+        <v>2</v>
+      </c>
+      <c r="H45" s="9">
+        <v>60</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>905</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
+        <v>535</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E0A641-51A7-4BF2-853E-7348B1610CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C57DFF8-ED74-4F73-85B5-6DE11C8F1754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2771,51 +2771,97 @@
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+      <c r="A46" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B46" s="9">
+        <v>420</v>
+      </c>
+      <c r="C46" s="9">
+        <v>60</v>
+      </c>
+      <c r="D46" s="9">
+        <v>120</v>
+      </c>
+      <c r="E46" s="9">
+        <v>35</v>
+      </c>
+      <c r="F46" s="9">
+        <v>350</v>
+      </c>
+      <c r="G46" s="9">
+        <v>7</v>
+      </c>
+      <c r="H46" s="9">
+        <v>60</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>1045</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
+        <v>395</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+      <c r="A47" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B47" s="9">
+        <v>450</v>
+      </c>
+      <c r="C47" s="9">
+        <v>70</v>
+      </c>
+      <c r="D47" s="9">
+        <v>180</v>
+      </c>
+      <c r="E47" s="9">
+        <v>50</v>
+      </c>
+      <c r="F47" s="9">
+        <v>200</v>
+      </c>
+      <c r="G47" s="9">
+        <v>4</v>
+      </c>
+      <c r="H47" s="9">
+        <v>50</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
+        <v>440</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
+      <c r="A48" s="8">
+        <v>46289</v>
+      </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -2837,7 +2883,9 @@
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
+      <c r="A49" s="8">
+        <v>46290</v>
+      </c>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
@@ -2859,7 +2907,9 @@
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
+      <c r="A50" s="8">
+        <v>46291</v>
+      </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
@@ -2881,7 +2931,9 @@
       <c r="N50" s="12"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
+      <c r="A51" s="8">
+        <v>46292</v>
+      </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -2903,7 +2955,9 @@
       <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
+      <c r="A52" s="8">
+        <v>46293</v>
+      </c>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
@@ -2925,7 +2979,9 @@
       <c r="N52" s="12"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
+      <c r="A53" s="8">
+        <v>46294</v>
+      </c>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
@@ -2947,7 +3003,9 @@
       <c r="N53" s="12"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
+      <c r="A54" s="8">
+        <v>46295</v>
+      </c>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
